--- a/Sanimo/configAppData/SanimoSheet.xlsx
+++ b/Sanimo/configAppData/SanimoSheet.xlsx
@@ -4,10 +4,11 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19635" windowHeight="7500"/>
+    <workbookView windowWidth="9390" windowHeight="7575" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="GRN" sheetId="1" r:id="rId1"/>
+    <sheet name="saleorder" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="50">
   <si>
     <t>supplier_name</t>
   </si>
@@ -132,19 +133,65 @@
   </si>
   <si>
     <t>20</t>
+  </si>
+  <si>
+    <t>Order_Date</t>
+  </si>
+  <si>
+    <t>Estimate_date</t>
+  </si>
+  <si>
+    <t>main_category</t>
+  </si>
+  <si>
+    <t>order_category</t>
+  </si>
+  <si>
+    <t>party_name</t>
+  </si>
+  <si>
+    <t>qlty_name</t>
+  </si>
+  <si>
+    <t>process</t>
+  </si>
+  <si>
+    <t>order_by</t>
+  </si>
+  <si>
+    <t>shade</t>
+  </si>
+  <si>
+    <t>order_qlty</t>
+  </si>
+  <si>
+    <t>Dyed</t>
+  </si>
+  <si>
+    <t>Program Order</t>
+  </si>
+  <si>
+    <t>VK INDUSTRIES</t>
+  </si>
+  <si>
+    <t>By Mail</t>
+  </si>
+  <si>
+    <t>MIX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ &quot;₹&quot;* #,##0.00_ ;_ &quot;₹&quot;* \-#,##0.00_ ;_ &quot;₹&quot;* &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="180" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -153,11 +200,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF222222"/>
+      <name val="Arial"/>
+      <charset val="1"/>
     </font>
     <font>
       <u/>
@@ -607,154 +660,158 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1184,31 +1241,126 @@
       <c r="K2" t="s">
         <v>30</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" s="4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+  <cols>
+    <col min="1" max="1" width="12.8571428571429" customWidth="1"/>
+    <col min="2" max="2" width="14.2857142857143" customWidth="1"/>
+    <col min="3" max="3" width="14.7142857142857" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15.75" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" spans="1:12">
+      <c r="A2" s="2" t="str">
+        <f ca="1">TEXT(TODAY(),"dd-mm-yyyy")</f>
+        <v>20-03-2026</v>
+      </c>
+      <c r="B2" s="3" t="str">
+        <f ca="1">TEXT(TODAY(),"dd-mm-yyyy")</f>
+        <v>20-03-2026</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="L2" s="5" t="s">
         <v>32</v>
       </c>
     </row>
